--- a/AAAGameData/DataTables/FishTable.xlsx
+++ b/AAAGameData/DataTables/FishTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="14">
   <si>
     <t>#</t>
   </si>
@@ -80,7 +80,10 @@
     <t>FishEntity</t>
   </si>
   <si>
-    <t>fish0</t>
+    <t>UI/Fish/fish0.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -1246,6 +1249,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="5"/>
   <cols>
     <col min="4" max="4" width="30.8181818181818" customWidth="1"/>
+    <col min="5" max="5" width="16.3636363636364" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1318,7 +1322,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="3:3">
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="3:3">
